--- a/tests/output/php81_export_test.xlsx
+++ b/tests/output/php81_export_test.xlsx
@@ -29,7 +29,7 @@
     <t>php81-export-ok</t>
   </si>
   <si>
-    <t>2026-03-02 14:26:05</t>
+    <t>2026-03-02 14:28:16</t>
   </si>
 </sst>
 </file>

--- a/tests/output/php81_export_test.xlsx
+++ b/tests/output/php81_export_test.xlsx
@@ -29,7 +29,7 @@
     <t>php81-export-ok</t>
   </si>
   <si>
-    <t>2026-03-02 14:28:16</t>
+    <t>2026-03-02 14:33:04</t>
   </si>
 </sst>
 </file>
